--- a/Unsorted/Павловск/восстановление/павловск_восстановление_подписи.xlsx
+++ b/Unsorted/Павловск/восстановление/павловск_восстановление_подписи.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="6" rupBuild="4505"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23232" windowHeight="13152" tabRatio="897" activeTab="5"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23232" windowHeight="13152" tabRatio="897" activeTab="10"/>
   </bookViews>
   <sheets>
     <sheet name="Лист9" sheetId="13" r:id="rId1"/>
@@ -313,57 +313,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Концепция реставрации Галереи Гонзаго Большого дворца Павловского дворцово-паркового ансамбля. Том 2. Фотофиксация
-ЦГАНТД СПб. Ф. Р-467. Оп. 315. Д. 261. Л. 9
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Концепция реставрации Галереи Гонзаго Большого дворца Павловского дворцово-паркового ансамбля. Том 2. Фотофиксация
-ЦГАНТД СПб. Ф. Р-467. Оп. 315. Д. 261. Л. 17
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Концепция реставрации Галереи Гонзаго Большого дворца Павловского дворцово-паркового ансамбля. Том 2. Фотофиксация
-ЦГАНТД СПб. Ф. Р-467. Оп. 315. Д. 261. Л. 21
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Концепция реставрации Галереи Гонзаго Большого дворца Павловского дворцово-паркового ансамбля. Том 2. Фотофиксация
-ЦГАНТД СПб. Ф. Р-467. Оп. 315. Д. 261. Л. 34
-</t>
-  </si>
-  <si>
     <t>ЦГАНТД СПб Ф. Р-467. Оп. 315. Д. 261. Л.9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Концепция реставрации Галереи Гонзаго Большого дворца Павловского дворцово-паркового ансамбля. Том 3. Предпроектные предложения
-ЦГАНТД СПб. Ф. Р-467. Оп. 315. Д. 262. Л.14
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Концепция реставрации Галереи Гонзаго Большого дворца Павловского дворцово-паркового ансамбля. Том 3. Предпроектные предложения
-ЦГАНТД СПб. Ф. Р-467. Оп. 315. Д. 262. Л.11
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Концепция реставрации Галереи Гонзаго Большого дворца Павловского дворцово-паркового ансамбля. Том 3. Предпроектные предложения
-ЦГАНТД СПб. Ф. Р-467. Оп. 315. Д. 262. Л.10
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Концепция реставрации Галереи Гонзаго Большого дворца Павловского дворцово-паркового ансамбля. Том 3.2. Предпроектные предложения
-ЦГАНТД СПб. Ф. Р-467. Оп. 315. Д. 263. Л. 19
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Концепция реставрации Галереи Гонзаго Большого дворца Павловского дворцово-паркового ансамбля. Том 3.2. Предпроектные предложения
-ЦГАНТД СПб. Ф. Р-467. Оп. 315. Д. 263. Л. 17
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Концепция реставрации Галереи Гонзаго Большого дворца Павловского дворцово-паркового ансамбля. Том 3.2. Предпроектные предложения
-ЦГАНТД СПб. Ф. Р-467. Оп. 315. Д. 263. Л. 15
-</t>
   </si>
   <si>
     <t xml:space="preserve">Общий вид Тронного зала Павловского дворца-музея во время реставрационных работ.1950-е гг., г. Павловск
@@ -781,21 +731,6 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Концепция реставрации Галереи Гонзаго Большого дворца Павловского дворцово-паркового ансамбля. Том 2. Фотофиксация
-ЦГАНТД СПб. Ф. Р-467. Оп. 315. Д. 261. Л. 9, 17, 21, 34
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Концепция реставрации Галереи Гонзаго Большого дворца Павловского дворцово-паркового ансамбля. Том 3. Предпроектные предложения
-ЦГАНТД СПб. Ф. Р-467. Оп. 315. Д. 262. Л.10, 11, 14
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Концепция реставрации Галереи Гонзаго Большого дворца Павловского дворцово-паркового ансамбля. Том 3.2. Предпроектные предложения
-ЦГАНТД СПб. Ф. Р-467. Оп. 315. Д. 263. Л. 15, 17, 19
-</t>
-  </si>
-  <si>
     <t xml:space="preserve">Справка о выполнении архитектурных обмеров интерьеров Большого дворца в Павловске с приложением сведений об их состоянии на июнь 1944 года
 КГИОП. П. 246-1. П-1080. Л. 141-154
 </t>
@@ -837,7 +772,91 @@
   </si>
   <si>
     <t xml:space="preserve">Фотофиксация живописного плафона Кавалерского зала Большого дворца Павловского дворцово-паркового ансамбля. 1987 г.
-ЦГАНТД СПб. Ф. Р-467. Оп. 315. Д. 251. Л. 1, 8, 12, 25
+ЦГАНТД СПб. Ф. Р-467. Оп. 315. Д. 251. Л. 1, 8, 13, 20, 25
+</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Концепция реставрации Галереи Гонзаго Большого дворца. Павловского дворцово-паркового ансамбля. Том 2. Фотофиксация
+ЦГАНТД СПб. Ф. Р-467. Оп. 315. Д. 261. Л. 9, 17, 21, 34</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Концепция реставрации Галереи Гонзаго Большого дворца. Павловского дворцово-паркового ансамбля. Том 2. Фотофиксация
+ЦГАНТД СПб. Ф. Р-467. Оп. 315. Д. 261. Л. 9
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Концепция реставрации Галереи Гонзаго Большого дворца. Павловского дворцово-паркового ансамбля. Том 2. Фотофиксация
+ЦГАНТД СПб. Ф. Р-467. Оп. 315. Д. 261. Л. 17
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Концепция реставрации Галереи Гонзаго Большого дворца. Павловского дворцово-паркового ансамбля. Том 2. Фотофиксация
+ЦГАНТД СПб. Ф. Р-467. Оп. 315. Д. 261. Л. 21
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Концепция реставрации Галереи Гонзаго Большого дворца. Павловского дворцово-паркового ансамбля. Том 2. Фотофиксация
+ЦГАНТД СПб. Ф. Р-467. Оп. 315. Д. 261. Л. 34
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Концепция реставрации Галереи Гонзаго Большого дворца. Павловского дворцово-паркового ансамбля. Том 3. Предпроектные предложения
+ЦГАНТД СПб. Ф. Р-467. Оп. 315. Д. 262. Л. 10, 11, 14
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Концепция реставрации Галереи Гонзаго Большого дворца. Павловского дворцово-паркового ансамбля. Том 3. Предпроектные предложения
+ЦГАНТД СПб. Ф. Р-467. Оп. 315. Д. 262. Л. 10
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Концепция реставрации Галереи Гонзаго Большого дворца. Павловского дворцово-паркового ансамбля. Том 3. Предпроектные предложения
+ЦГАНТД СПб. Ф. Р-467. Оп. 315. Д. 262. Л. 11
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Концепция реставрации Галереи Гонзаго Большого дворца. Павловского дворцово-паркового ансамбля. Том 3. Предпроектные предложения
+ЦГАНТД СПб. Ф. Р-467. Оп. 315. Д. 262. Л. 14
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Концепция реставрации Галереи Гонзаго Большого дворца. Павловского дворцово-паркового ансамбля. Том 3.2. Предпроектные предложения
+ЦГАНТД СПб. Ф. Р-467. Оп. 315. Д. 263. Л. 15, 17, 19
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Концепция реставрации Галереи Гонзаго Большого дворца. Павловского дворцово-паркового ансамбля. Том 3.2. Предпроектные предложения
+ЦГАНТД СПб. Ф. Р-467. Оп. 315. Д. 263. Л. 15
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Концепция реставрации Галереи Гонзаго Большого дворца. Павловского дворцово-паркового ансамбля. Том 3.2. Предпроектные предложения
+ЦГАНТД СПб. Ф. Р-467. Оп. 315. Д. 263. Л. 17
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Концепция реставрации Галереи Гонзаго Большого дворца. Павловского дворцово-паркового ансамбля. Том 3.2. Предпроектные предложения
+ЦГАНТД СПб. Ф. Р-467. Оп. 315. Д. 263. Л. 19
 </t>
   </si>
 </sst>
@@ -845,12 +864,20 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="3">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -869,6 +896,19 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -904,22 +944,28 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1192,7 +1238,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1234,138 +1280,138 @@
     </row>
     <row r="4" spans="1:3" ht="72">
       <c r="A4" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="C4" s="6"/>
     </row>
     <row r="5" spans="1:3" ht="72">
       <c r="A5" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="C5" s="6"/>
     </row>
     <row r="6" spans="1:3" ht="72">
       <c r="A6" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="C6" s="6"/>
     </row>
     <row r="7" spans="1:3" ht="86.4">
       <c r="A7" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="86.4">
       <c r="A8" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="57.6">
       <c r="A9" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="72">
       <c r="A10" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="57.6">
       <c r="A11" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="57.6">
       <c r="A12" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="57.6">
       <c r="A13" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="57.6">
       <c r="A14" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="C14" s="6"/>
     </row>
     <row r="15" spans="1:3" ht="57.6">
       <c r="A15" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="C15" s="6"/>
     </row>
     <row r="16" spans="1:3" ht="72">
       <c r="A16" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="C16" s="6"/>
     </row>
     <row r="17" spans="1:3" ht="57.6">
       <c r="A17" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="C17" s="6"/>
     </row>
     <row r="18" spans="1:3" ht="57.6">
       <c r="A18" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="C18" s="6"/>
     </row>
     <row r="19" spans="1:3" ht="72">
       <c r="A19" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="C19" s="6"/>
     </row>
@@ -1398,8 +1444,8 @@
       <c r="A2" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>184</v>
+      <c r="B2" s="8" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1414,24 +1460,24 @@
       <c r="A4" t="s">
         <v>31</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>79</v>
+      <c r="B4" s="8" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="72">
       <c r="A5" t="s">
         <v>32</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>78</v>
+      <c r="B5" s="8" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="72">
       <c r="A6" t="s">
         <v>33</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>77</v>
+      <c r="B6" s="8" t="s">
+        <v>190</v>
       </c>
     </row>
   </sheetData>
@@ -1463,8 +1509,8 @@
       <c r="A2" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>185</v>
+      <c r="B2" s="8" t="s">
+        <v>191</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1479,24 +1525,24 @@
       <c r="A4" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>82</v>
+      <c r="B4" s="8" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="72">
       <c r="A5" t="s">
         <v>35</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>81</v>
+      <c r="B5" s="8" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="72">
       <c r="A6" t="s">
         <v>36</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>80</v>
+      <c r="B6" s="8" t="s">
+        <v>194</v>
       </c>
     </row>
   </sheetData>
@@ -1529,7 +1575,7 @@
         <v>39</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>186</v>
+        <v>173</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1542,114 +1588,114 @@
     </row>
     <row r="4" spans="1:2" ht="72">
       <c r="A4" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="72">
       <c r="A5" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="72">
       <c r="A6" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="72">
       <c r="A7" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="72">
       <c r="A8" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="72">
       <c r="A9" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="72">
       <c r="A10" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="72">
       <c r="A11" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="72">
       <c r="A12" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="72">
       <c r="A13" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="72">
       <c r="A14" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="72">
       <c r="A15" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="72">
       <c r="A16" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="72">
       <c r="A17" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -1685,7 +1731,7 @@
         <v>39</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>187</v>
+        <v>174</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1698,18 +1744,18 @@
     </row>
     <row r="4" spans="1:2" ht="57.6">
       <c r="A4" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="57.6">
       <c r="A5" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
     </row>
   </sheetData>
@@ -1742,7 +1788,7 @@
         <v>39</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>188</v>
+        <v>175</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1755,26 +1801,26 @@
     </row>
     <row r="4" spans="1:2" ht="86.4">
       <c r="A4" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="86.4">
       <c r="A5" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="86.4">
       <c r="A6" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
     </row>
   </sheetData>
@@ -1807,7 +1853,7 @@
         <v>39</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>189</v>
+        <v>176</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1820,18 +1866,18 @@
     </row>
     <row r="4" spans="1:2" ht="57.6">
       <c r="A4" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="57.6">
       <c r="A5" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
     </row>
   </sheetData>
@@ -1864,7 +1910,7 @@
         <v>39</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>190</v>
+        <v>177</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1877,18 +1923,18 @@
     </row>
     <row r="4" spans="1:2" ht="43.2">
       <c r="A4" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="43.2">
       <c r="A5" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
     </row>
   </sheetData>
@@ -1921,7 +1967,7 @@
         <v>39</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>191</v>
+        <v>178</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1934,34 +1980,34 @@
     </row>
     <row r="4" spans="1:2" ht="57.6">
       <c r="A4" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="57.6">
       <c r="A5" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="57.6">
       <c r="A6" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="57.6">
       <c r="A7" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>163</v>
+        <v>153</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1997,7 +2043,7 @@
         <v>39</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>192</v>
+        <v>179</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -2010,18 +2056,18 @@
     </row>
     <row r="4" spans="1:2" ht="72">
       <c r="A4" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="72">
       <c r="A5" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
     </row>
   </sheetData>
@@ -2054,7 +2100,7 @@
         <v>39</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -2067,18 +2113,18 @@
     </row>
     <row r="4" spans="1:2" ht="86.4">
       <c r="A4" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="86.4">
       <c r="A5" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
     </row>
   </sheetData>
@@ -2111,7 +2157,7 @@
         <v>39</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -2192,7 +2238,7 @@
         <v>39</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -2266,7 +2312,7 @@
         <v>39</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -2347,7 +2393,7 @@
         <v>39</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>180</v>
+        <v>170</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -2420,7 +2466,7 @@
         <v>39</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>194</v>
+        <v>181</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -2501,7 +2547,7 @@
         <v>39</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -2566,7 +2612,7 @@
         <v>39</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -2630,8 +2676,8 @@
       <c r="A2" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>183</v>
+      <c r="B2" s="7" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -2644,37 +2690,38 @@
     </row>
     <row r="4" spans="1:2" ht="57.6">
       <c r="A4" t="s">
-        <v>76</v>
-      </c>
-      <c r="B4" s="2" t="s">
         <v>72</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="57.6">
       <c r="A5" t="s">
         <v>28</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>73</v>
+      <c r="B5" s="8" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="57.6">
       <c r="A6" t="s">
         <v>29</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>74</v>
+      <c r="B6" s="8" t="s">
+        <v>185</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="57.6">
       <c r="A7" t="s">
         <v>30</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>75</v>
+      <c r="B7" s="8" t="s">
+        <v>186</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Unsorted/Павловск/восстановление/павловск_восстановление_подписи.xlsx
+++ b/Unsorted/Павловск/восстановление/павловск_восстановление_подписи.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="6" rupBuild="4505"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23232" windowHeight="13152" tabRatio="897" activeTab="10"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23232" windowHeight="13152" tabRatio="897"/>
   </bookViews>
   <sheets>
     <sheet name="Лист9" sheetId="13" r:id="rId1"/>
@@ -26,6 +26,9 @@
     <sheet name="Лист15" sheetId="19" r:id="rId17"/>
     <sheet name="Лист16" sheetId="20" r:id="rId18"/>
     <sheet name="Лист17" sheetId="21" r:id="rId19"/>
+    <sheet name="Лист18" sheetId="22" r:id="rId20"/>
+    <sheet name="Лист19" sheetId="23" r:id="rId21"/>
+    <sheet name="Лист20" sheetId="24" r:id="rId22"/>
   </sheets>
   <calcPr calcId="124519"/>
   <extLst xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main">
@@ -37,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="282">
   <si>
     <t>подпись</t>
   </si>
@@ -858,6 +861,420 @@
     <t xml:space="preserve">Концепция реставрации Галереи Гонзаго Большого дворца. Павловского дворцово-паркового ансамбля. Том 3.2. Предпроектные предложения
 ЦГАНТД СПб. Ф. Р-467. Оп. 315. Д. 263. Л. 19
 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Трескин А.В.
+Павловский дворец. Греческий зал. Эскиз росписи плафона. 1965 г.
+НВК-7290
+Государственный музей-заповедник «Павловск»
+</t>
+  </si>
+  <si>
+    <t>1. Трескин А.В. Павловский дворец. Греческий зал. Эскиз росписи плафона. НВК-7290_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Павловский дворец. Греческий зал. В процессе реставрации. 1967 г.
+Фотография
+Государственный музей-заповедник «Павловск»
+</t>
+  </si>
+  <si>
+    <t>2. Павловский дворец. Греческий зал. В процессе реставрации. 1967 г.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Казаков Я.А.
+Павловский дворец. Галерея Гонзаго. Эскиз воссоздания живописи. Фреска № 1. 1973 г.
+НВК-10235
+Государственный музей-заповедник «Павловск»
+</t>
+  </si>
+  <si>
+    <t>4. Казаков Я.А. Павловский дворец. Галерея Гонзаго. Эскиз воссоздания живописи. Фреска № 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Казаков Я.А. 
+Павловский дворец. Эскиз воссоздания живописи на потолке Галереи Гонзаго. 1973 г.
+НВК-10233
+Государственный музей-заповедник «Павловск»
+</t>
+  </si>
+  <si>
+    <t>5. Казаков Я.А. Эскиз воссоздания живописи на потолке Галереи Гонз. НВК-10233_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Обмерный чертеж. Павловский дворец. Тронный зал. Развертка стены. Лист № 2. 1946 г.
+НВК-1858/4
+Государственный музей-заповедник «Павловск»
+</t>
+  </si>
+  <si>
+    <t>6. Обмерный чертеж. Павловский дворец. Тронный зал. Развертка стены. Лист № 2. НВК-1858-4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Обмерный чертеж. Павловский дворец. Тронный зал. Развертка стены 'Д'. Лист 1-3. 1946 г.
+НВК-1858/3
+Государственный музей-заповедник «Павловск»
+</t>
+  </si>
+  <si>
+    <t>7. Обмерный чертеж.. Павловский дворец. Тронный зал. Развертка стены 'Д'. Лист 1.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Попова-Гунич С.В.,Капцюг И.Г., Казанская Е.В.
+Обмерные кроки. Павловский дворец. Тронный зал. Обмер и состояние северо-западной ниши. 1955 г.
+НВК-4464
+Государственный музей-заповедник «Павловск»
+</t>
+  </si>
+  <si>
+    <t>8. Попова-Гунич С.В._ Капцюг И.Г._ Казанская Е.В. Обмерные кроки. Павловский дворец</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Трескин А.В.
+Павловский дворец. Тронный зал. Эскиз-проект архитектурно-художественного решения отделки. 1950-е гг.
+Акварель
+НВК-12850/2
+Государственный музей-заповедник «Павловск»
+</t>
+  </si>
+  <si>
+    <t>9. Трескин А.В. Павловский дворец. Тронный зал. Эскиз-проект</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Мальцева Н.И., Шабалкина Р.
+Кариатида из Тронного зала. Модель из пластилина. 1960-е гг.
+НВК-22324
+Государственный музей-заповедник «Павловск»
+</t>
+  </si>
+  <si>
+    <t>10. Мальцева Н.И._ Шабалкина Р. Кариатида из Тронного зала. Модель из пластилина</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Громова Н.И. 
+Павловский дворец. Итальянский зал IV. Эталон. Позолота лепных деталей. 1946 г.
+Чертеж
+НВК-1362-1
+Государственный музей-заповедник «Павловск»
+</t>
+  </si>
+  <si>
+    <t>11. Громова Н.И. Павловский дворец. Итальянский зал IV. Эталон.  НВК-1362-1</t>
+  </si>
+  <si>
+    <t>12. Громова Н.И. Павловский дворец. Итальянский зал IV. Эталон. НВК-1362-3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Громова Н.И. 
+Павловский дворец. Итальянский зал IV. Эталон. Позолота лепных деталей.1946 г.
+Чертеж
+НВК-1362-3
+Государственный музей-заповедник «Павловск»
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Павловский дворец. Итальянский зал.1961 г.
+В процессе реставрации – золочение розеток купола
+Фотография
+Государственный музей-заповедник «Павловск»
+</t>
+  </si>
+  <si>
+    <t>13. Павловский дворец. Итальянский зал. 1961 г. в процессе реставрации</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Олейник Ф.Ф. 
+Павловский дворец. Белая столовая. Фрагмент фриза. 1944 г.
+Акварель
+НВК-12494
+Государственный музей-заповедник «Павловск»
+</t>
+  </si>
+  <si>
+    <t>14. Олейник Ф.Ф. Павловский дворец. Белая столовая. Фрагмент фриза. НВК-12494_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Павловский дворец. Белая столовая. В процессе реставрации. 1968 г.
+Фотография
+Государственный музей-заповедник «Павловск»
+</t>
+  </si>
+  <si>
+    <t>15. Павловский дворец. Белая столовая. В процессе реставрации. 1968 г.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Монтажный лист. Павловский дворец. Экспозиция Белой столовой. Развертка западной стены. 1960-е гг.
+НВК-15706/2
+Государственный музей-заповедник «Павловск»
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Синица Ю.И.
+Чертеж рабочий. Павловский дворец. Библиотека Павла I. Развертка западной стены. Порезки двери.1960-е гг.
+НВК-5451
+Государственный музей-заповедник «Павловск»
+</t>
+  </si>
+  <si>
+    <t>17. Синица Ю.И. Чертеж рабочий. Павловский дворец. Библиотека Павл. НВК-5451_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Трескин А.В.
+Павловский дворец. Библиотека Павла. Эскиз росписи плафона «Истина изгоняющая пороки».1962г.
+НВК-7299
+Государственный музей-заповедник «Павловск»
+</t>
+  </si>
+  <si>
+    <t>18. Трескин А.В. Павловский дворец. Библиотека Павла. Эскиз росписи. НВК-7299_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Павловский дворец. Кавалерский зал. 1947 г.
+Фотография
+Государственный музей-заповедник «Павловск»
+</t>
+  </si>
+  <si>
+    <t>19. Павловский дворец. Кавалерский зал. 1947 г.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Павловский дворец. Кавалерский зал. 1956 г.
+Фотография
+Государственный музей-заповедник «Павловск»
+</t>
+  </si>
+  <si>
+    <t>20. Павловский дворец. Кавалерский зал. 1956 г.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Левичева К.
+Павловский дворец. Предцерковный (Кавалерский) зал. Барельеф в арке портала. Лист № 7. 1947 г.
+НВК-1624
+Государственный музей-заповедник «Павловск»
+</t>
+  </si>
+  <si>
+    <t>21. Левичева К. Павловский дворец. Предцерковный зал. Барельеф в арке портала. Лист № 7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Барельеф для арки портала Кавалерского зала. Воссозданный.1970-е гг.
+Фотография
+Государственный музей-заповедник «Павловск»
+</t>
+  </si>
+  <si>
+    <t>22. Барельеф для арки портала Кавалерского зала. Воссозданный.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Павловский дворец. 1954 г.
+Фотография
+Государственный музей-заповедник «Павловск»
+</t>
+  </si>
+  <si>
+    <t>23. Павловский дворец. 1954 г.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Павловский дворец. Фасад со стороны Парадного двора
+НВК-1466
+Государственный музей-заповедник «Павловск»
+</t>
+  </si>
+  <si>
+    <t>24. Павловский дворец. Фасад со стороны Парадного двора. НВК-1466</t>
+  </si>
+  <si>
+    <t>Большой дворец сегодня</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Павловский дворец. 2010-е гг.
+Современный вид.
+Фотография
+Государственный музей-заповедник «Павловск»
+</t>
+  </si>
+  <si>
+    <t>25. Павловский дворец. 2010-е гг. Современный вид</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Павловский дворец. Кавалерский зал. 2000-е гг.
+Современный вид.
+Фотография
+Государственный музей-заповедник «Павловск»
+</t>
+  </si>
+  <si>
+    <t>26. Павловский дворец. Кавалерский зал. 2000-е гг. Современный вид</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Павловский дворец. Библиотека Павла. 2000-е гг.
+Современный вид
+Фотография
+Государственный музей-заповедник «Павловск»
+</t>
+  </si>
+  <si>
+    <t>27. Павловский дворец. Библиотека Павла. 2000-е гг. Современный вид</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Павловский дворец. Библиотека Павла. Потолок. 2010-е гг.
+Современный вид
+Фотография
+Государственный музей-заповедник «Павловск»
+</t>
+  </si>
+  <si>
+    <t>28. Павловский дворец. Библиотека Павла. Потолок. 2010-е гг.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Павловский дворец. Белая столовая. 2000-е гг.
+Современный вид
+Фотография
+Государственный музей-заповедник «Павловск»
+</t>
+  </si>
+  <si>
+    <t>29. Павловский дворец. Белая столовая. 2000-е гг.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Павловский дворец. Итальянский зал (купол). 2000-е гг.
+Современный вид
+Фотография
+Государственный музей-заповедник «Павловск»
+</t>
+  </si>
+  <si>
+    <t>30. Павловский дворец. Итальянский зал (купол). 2000-е гг.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Павловский дворец. Итальянский зал. 2000-е гг.
+Современный вид
+Фотография
+Государственный музей-заповедник «Павловск»
+</t>
+  </si>
+  <si>
+    <t>31. Павловский дворец. Итальянский зал. 2000-е гг.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Павловский дворец. Греческий зал. 2000-е гг.
+Современный вид
+Фотография
+Государственный музей-заповедник «Павловск»
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Галерея Гонзаго. 2015 г.
+Современный вид
+Фотография
+Государственный музей-заповедник «Павловск»
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Павловский дворец. Тронный зал. 2000-е гг.
+Современный вид
+Фотография
+Государственный музей-заповедник «Павловск»
+</t>
+  </si>
+  <si>
+    <t>32. Павловский дворец. Греческий зал. Современный вид</t>
+  </si>
+  <si>
+    <t>33. Галерея Гонзаго. Современный вид</t>
+  </si>
+  <si>
+    <t>34. Тронный зал. Современный вид</t>
+  </si>
+  <si>
+    <t>Мавзолей Павла I</t>
+  </si>
+  <si>
+    <t>Старое Шале</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Кроки. Мавзолей Павла I; деталь № 1; барельеф пьедестала памятника Павлу I. Работа студии Академии Художеств. 1946 г.
+Чертеж
+Государственный музей-заповедник «Павловск»
+</t>
+  </si>
+  <si>
+    <t>35. Кроки. Мавзолей Павла I; деталь № 1; барельеф пьедестала памятника Павлу I.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Мавзолей Павла I.2000-е гг.
+Современный вид
+Государственный музей-заповедник «Павловск»
+</t>
+  </si>
+  <si>
+    <t>36. Мавзолей Павла I. Современный вид</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Старое Шале. До 1917 г.
+Фотография
+Государственный музей-заповедник «Павловск»
+</t>
+  </si>
+  <si>
+    <t>37. Старое Шале. До 1917 г.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Старое Шале. Интерьер. До 1917 г.
+Фотография
+Государственный музей-заповедник «Павловск»
+</t>
+  </si>
+  <si>
+    <t>38. Старое Шале. Интерьер. До 1922 г.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Старое Шале. Интерьер. До 1922 г.
+Фотография
+Государственный музей-заповедник «Павловск»
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Старое Шале. Роспись стены. До 1917 г.
+Фотография
+Государственный музей-заповедник «Павловск»
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Старое Шале. Двери. Эскиз. 2024 г.
+Фотография
+Государственный музей-заповедник «Павловск»
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Эскиз интерьера Старого Шале. 2024 г.
+Фотография
+Государственный музей-заповедник «Павловск»
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Старое Шале в процессе реставрации. 2025 г.
+Фотография
+Государственный музей-заповедник «Павловск»
+</t>
+  </si>
+  <si>
+    <t>39. Старое Шале. Роспись стены. До 1917 г.</t>
+  </si>
+  <si>
+    <t>40. Старое Шале. Двери. Эскиз. 2024 г.</t>
+  </si>
+  <si>
+    <t>41. Эскиз интерьера Старого Шале. 2024 г.</t>
+  </si>
+  <si>
+    <t>42. Старое Шале в процессе реставрации. 2025 г.</t>
+  </si>
+  <si>
+    <t>43. Старое Шале в процессе реставрации. 2025 г.</t>
+  </si>
+  <si>
+    <t>44. Старое Шале в процессе реставрации. 2025 г.</t>
   </si>
 </sst>
 </file>
@@ -912,7 +1329,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -931,6 +1348,30 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFA3FF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -944,7 +1385,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -966,12 +1407,28 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFFFA3FF"/>
+      <color rgb="FFFF66FF"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1238,7 +1695,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1249,7 +1706,7 @@
   <sheetPr>
     <tabColor theme="5" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C42"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="38.89453125" customWidth="1"/>
@@ -1414,6 +1871,188 @@
         <v>91</v>
       </c>
       <c r="C19" s="6"/>
+    </row>
+    <row r="20" spans="1:3" ht="72">
+      <c r="A20" t="s">
+        <v>196</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="57.6">
+      <c r="A21" t="s">
+        <v>198</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="86.4">
+      <c r="A22" t="s">
+        <v>200</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="86.4">
+      <c r="A23" t="s">
+        <v>202</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="72">
+      <c r="A24" t="s">
+        <v>204</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="72">
+      <c r="A25" t="s">
+        <v>206</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="86.4">
+      <c r="A26" t="s">
+        <v>208</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="100.8">
+      <c r="A27" t="s">
+        <v>210</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="72">
+      <c r="A28" t="s">
+        <v>212</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="100.8">
+      <c r="A29" t="s">
+        <v>214</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="100.8">
+      <c r="A30" t="s">
+        <v>215</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="72">
+      <c r="A31" t="s">
+        <v>218</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="86.4">
+      <c r="A32" t="s">
+        <v>220</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" ht="72">
+      <c r="A33" t="s">
+        <v>222</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="72">
+      <c r="B34" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="C34" s="9"/>
+    </row>
+    <row r="35" spans="1:3" ht="86.4">
+      <c r="A35" t="s">
+        <v>225</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" ht="86.4">
+      <c r="A36" t="s">
+        <v>227</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" ht="57.6">
+      <c r="A37" t="s">
+        <v>229</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" ht="57.6">
+      <c r="A38" t="s">
+        <v>231</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" ht="86.4">
+      <c r="A39" t="s">
+        <v>233</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" ht="72">
+      <c r="A40" t="s">
+        <v>235</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" ht="57.6">
+      <c r="A41" t="s">
+        <v>237</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" ht="57.6">
+      <c r="A42" t="s">
+        <v>239</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>238</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2210,6 +2849,290 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <tabColor theme="4" tint="0.39997558519241921"/>
+  </sheetPr>
+  <dimension ref="A1:B13"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="38.89453125" customWidth="1"/>
+    <col min="2" max="2" width="58.7890625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="15.6">
+      <c r="A1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="10" t="s">
+        <v>240</v>
+      </c>
+      <c r="B2" s="2"/>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="72">
+      <c r="A4" t="s">
+        <v>242</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="72">
+      <c r="A5" t="s">
+        <v>244</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="72">
+      <c r="A6" t="s">
+        <v>246</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="72">
+      <c r="A7" t="s">
+        <v>248</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="72">
+      <c r="A8" t="s">
+        <v>250</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="72">
+      <c r="A9" t="s">
+        <v>252</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="72">
+      <c r="A10" t="s">
+        <v>254</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="72">
+      <c r="A11" t="s">
+        <v>258</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="72">
+      <c r="A12" t="s">
+        <v>259</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="72">
+      <c r="A13" t="s">
+        <v>260</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>257</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <tabColor rgb="FFFF66FF"/>
+  </sheetPr>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="38.89453125" customWidth="1"/>
+    <col min="2" max="2" width="58.7890625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="15.6">
+      <c r="A1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="12" t="s">
+        <v>261</v>
+      </c>
+      <c r="B2" s="2"/>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="72">
+      <c r="A4" t="s">
+        <v>264</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="57.6">
+      <c r="A5" t="s">
+        <v>266</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>265</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <tabColor rgb="FF92D050"/>
+  </sheetPr>
+  <dimension ref="A1:C12"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="38.89453125" customWidth="1"/>
+    <col min="2" max="2" width="58.7890625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="15.6">
+      <c r="A1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="11" t="s">
+        <v>262</v>
+      </c>
+      <c r="B2" s="2"/>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="57.6">
+      <c r="A4" t="s">
+        <v>268</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="57.6">
+      <c r="B5" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="C5" s="9"/>
+    </row>
+    <row r="6" spans="1:3" ht="57.6">
+      <c r="A6" t="s">
+        <v>270</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="57.6">
+      <c r="A7" t="s">
+        <v>276</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="57.6">
+      <c r="A8" t="s">
+        <v>277</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="57.6">
+      <c r="A9" t="s">
+        <v>278</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="57.6">
+      <c r="A10" t="s">
+        <v>279</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="57.6">
+      <c r="A11" t="s">
+        <v>280</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="57.6">
+      <c r="A12" t="s">
+        <v>281</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>275</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/Unsorted/Павловск/восстановление/павловск_восстановление_подписи.xlsx
+++ b/Unsorted/Павловск/восстановление/павловск_восстановление_подписи.xlsx
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="284">
   <si>
     <t>подпись</t>
   </si>
@@ -1275,6 +1275,12 @@
   </si>
   <si>
     <t>44. Старое Шале в процессе реставрации. 2025 г.</t>
+  </si>
+  <si>
+    <t>38. Старое Шале. Интерьер. До 1917 г.</t>
+  </si>
+  <si>
+    <t>167441~1</t>
   </si>
 </sst>
 </file>
@@ -1329,7 +1335,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1345,12 +1351,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1385,7 +1385,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1407,14 +1407,13 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1695,7 +1694,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1985,10 +1984,13 @@
       </c>
     </row>
     <row r="34" spans="1:3" ht="72">
+      <c r="A34" t="s">
+        <v>283</v>
+      </c>
       <c r="B34" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="C34" s="9"/>
+      <c r="C34" s="6"/>
     </row>
     <row r="35" spans="1:3" ht="86.4">
       <c r="A35" t="s">
@@ -2873,7 +2875,7 @@
       </c>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>240</v>
       </c>
       <c r="B2" s="2"/>
@@ -2992,7 +2994,7 @@
       </c>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="11" t="s">
         <v>261</v>
       </c>
       <c r="B2" s="2"/>
@@ -3047,7 +3049,7 @@
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="10" t="s">
         <v>262</v>
       </c>
       <c r="B2" s="2"/>
@@ -3069,10 +3071,13 @@
       </c>
     </row>
     <row r="5" spans="1:3" ht="57.6">
+      <c r="A5" t="s">
+        <v>282</v>
+      </c>
       <c r="B5" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="C5" s="9"/>
+      <c r="C5" s="6"/>
     </row>
     <row r="6" spans="1:3" ht="57.6">
       <c r="A6" t="s">

--- a/Unsorted/Павловск/восстановление/павловск_восстановление_подписи.xlsx
+++ b/Unsorted/Павловск/восстановление/павловск_восстановление_подписи.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="6" rupBuild="4505"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23232" windowHeight="13152" tabRatio="897"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23232" windowHeight="13152" tabRatio="897" activeTab="21"/>
   </bookViews>
   <sheets>
     <sheet name="Лист9" sheetId="13" r:id="rId1"/>
@@ -1226,9 +1226,6 @@
 </t>
   </si>
   <si>
-    <t>38. Старое Шале. Интерьер. До 1922 г.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Старое Шале. Интерьер. До 1922 г.
 Фотография
 Государственный музей-заповедник «Павловск»
@@ -1281,6 +1278,9 @@
   </si>
   <si>
     <t>167441~1</t>
+  </si>
+  <si>
+    <t>45. Старое Шале. Интерьер. До 1922 г.</t>
   </si>
 </sst>
 </file>
@@ -1694,7 +1694,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1985,7 +1985,7 @@
     </row>
     <row r="34" spans="1:3" ht="72">
       <c r="A34" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>223</v>
@@ -3072,7 +3072,7 @@
     </row>
     <row r="5" spans="1:3" ht="57.6">
       <c r="A5" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>269</v>
@@ -3081,58 +3081,58 @@
     </row>
     <row r="6" spans="1:3" ht="57.6">
       <c r="A6" t="s">
+        <v>283</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>270</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>271</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="57.6">
       <c r="A7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="57.6">
       <c r="A8" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="57.6">
       <c r="A9" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="57.6">
       <c r="A10" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="57.6">
       <c r="A11" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="57.6">
       <c r="A12" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
   </sheetData>

--- a/Unsorted/Павловск/восстановление/павловск_восстановление_подписи.xlsx
+++ b/Unsorted/Павловск/восстановление/павловск_восстановление_подписи.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="6" rupBuild="4505"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23232" windowHeight="13152" tabRatio="897" activeTab="21"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23232" windowHeight="13152" tabRatio="897"/>
   </bookViews>
   <sheets>
     <sheet name="Лист9" sheetId="13" r:id="rId1"/>
@@ -393,18 +393,6 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Павловский дворец. Новая конструкция и новая кладка купола дворца. 1949 г.
-Автор съемки:Григорьев А.А.
-КГИОП.№27258
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Павловский дворец. Общий вид главного фасада. 1973 г.
-Автор съемки:А. Григорьев
-КГИОП. № 102303
-</t>
-  </si>
-  <si>
     <t xml:space="preserve">Павловский дворец. Панорама реки Славянки. 1972 г.
 Автор съемки:А. Григорьев
 КГИОП. № 100477
@@ -1281,6 +1269,18 @@
   </si>
   <si>
     <t>45. Старое Шале. Интерьер. До 1922 г.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Павловский дворец. Новая конструкция и новая кладка купола дворца. 1949 г.
+Автор съемки: Григорьев А.А.
+КГИОП.№27258
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Павловский дворец. Общий вид главного фасада. 1973 г.
+Автор съемки: А. Григорьев
+КГИОП. № 102303
+</t>
   </si>
 </sst>
 </file>
@@ -1694,7 +1694,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1763,7 +1763,7 @@
     </row>
     <row r="7" spans="1:3" ht="86.4">
       <c r="A7" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>79</v>
@@ -1771,7 +1771,7 @@
     </row>
     <row r="8" spans="1:3" ht="86.4">
       <c r="A8" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>80</v>
@@ -1779,7 +1779,7 @@
     </row>
     <row r="9" spans="1:3" ht="57.6">
       <c r="A9" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>81</v>
@@ -1787,7 +1787,7 @@
     </row>
     <row r="10" spans="1:3" ht="72">
       <c r="A10" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>82</v>
@@ -1795,7 +1795,7 @@
     </row>
     <row r="11" spans="1:3" ht="57.6">
       <c r="A11" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>83</v>
@@ -1803,7 +1803,7 @@
     </row>
     <row r="12" spans="1:3" ht="57.6">
       <c r="A12" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>84</v>
@@ -1811,7 +1811,7 @@
     </row>
     <row r="13" spans="1:3" ht="57.6">
       <c r="A13" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>85</v>
@@ -1819,7 +1819,7 @@
     </row>
     <row r="14" spans="1:3" ht="57.6">
       <c r="A14" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>86</v>
@@ -1828,7 +1828,7 @@
     </row>
     <row r="15" spans="1:3" ht="57.6">
       <c r="A15" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>87</v>
@@ -1837,223 +1837,223 @@
     </row>
     <row r="16" spans="1:3" ht="72">
       <c r="A16" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>88</v>
+        <v>282</v>
       </c>
       <c r="C16" s="6"/>
     </row>
     <row r="17" spans="1:3" ht="57.6">
       <c r="A17" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>89</v>
+        <v>283</v>
       </c>
       <c r="C17" s="6"/>
     </row>
     <row r="18" spans="1:3" ht="57.6">
       <c r="A18" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C18" s="6"/>
     </row>
     <row r="19" spans="1:3" ht="72">
       <c r="A19" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C19" s="6"/>
     </row>
     <row r="20" spans="1:3" ht="72">
       <c r="A20" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="57.6">
       <c r="A21" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="86.4">
       <c r="A22" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="86.4">
       <c r="A23" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="72">
       <c r="A24" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="72">
       <c r="A25" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="86.4">
       <c r="A26" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="100.8">
       <c r="A27" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="72">
       <c r="A28" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="100.8">
       <c r="A29" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="100.8">
       <c r="A30" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="72">
       <c r="A31" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="86.4">
       <c r="A32" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="72">
       <c r="A33" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="72">
       <c r="A34" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C34" s="6"/>
     </row>
     <row r="35" spans="1:3" ht="86.4">
       <c r="A35" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="86.4">
       <c r="A36" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="57.6">
       <c r="A37" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="57.6">
       <c r="A38" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="86.4">
       <c r="A39" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="40" spans="1:3" ht="72">
       <c r="A40" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="57.6">
       <c r="A41" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="57.6">
       <c r="A42" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
   </sheetData>
@@ -2086,7 +2086,7 @@
         <v>39</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -2102,7 +2102,7 @@
         <v>31</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="72">
@@ -2110,7 +2110,7 @@
         <v>32</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="72">
@@ -2118,7 +2118,7 @@
         <v>33</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
   </sheetData>
@@ -2151,7 +2151,7 @@
         <v>39</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -2167,7 +2167,7 @@
         <v>34</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="72">
@@ -2175,7 +2175,7 @@
         <v>35</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="72">
@@ -2183,7 +2183,7 @@
         <v>36</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
   </sheetData>
@@ -2216,7 +2216,7 @@
         <v>39</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -2229,114 +2229,114 @@
     </row>
     <row r="4" spans="1:2" ht="72">
       <c r="A4" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="72">
       <c r="A5" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="72">
       <c r="A6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="72">
       <c r="A7" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="72">
       <c r="A8" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="72">
       <c r="A9" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="72">
       <c r="A10" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="72">
       <c r="A11" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="72">
       <c r="A12" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="72">
       <c r="A13" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="72">
       <c r="A14" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="72">
       <c r="A15" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="72">
       <c r="A16" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="72">
       <c r="A17" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -2372,7 +2372,7 @@
         <v>39</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -2385,18 +2385,18 @@
     </row>
     <row r="4" spans="1:2" ht="57.6">
       <c r="A4" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="57.6">
       <c r="A5" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
   </sheetData>
@@ -2429,7 +2429,7 @@
         <v>39</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -2442,26 +2442,26 @@
     </row>
     <row r="4" spans="1:2" ht="86.4">
       <c r="A4" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="86.4">
       <c r="A5" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="86.4">
       <c r="A6" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
   </sheetData>
@@ -2494,7 +2494,7 @@
         <v>39</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -2507,18 +2507,18 @@
     </row>
     <row r="4" spans="1:2" ht="57.6">
       <c r="A4" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="57.6">
       <c r="A5" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
   </sheetData>
@@ -2551,7 +2551,7 @@
         <v>39</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -2564,18 +2564,18 @@
     </row>
     <row r="4" spans="1:2" ht="43.2">
       <c r="A4" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="43.2">
       <c r="A5" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
   </sheetData>
@@ -2608,7 +2608,7 @@
         <v>39</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -2621,34 +2621,34 @@
     </row>
     <row r="4" spans="1:2" ht="57.6">
       <c r="A4" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="57.6">
       <c r="A5" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="57.6">
       <c r="A6" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="57.6">
       <c r="A7" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -2684,7 +2684,7 @@
         <v>39</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -2697,18 +2697,18 @@
     </row>
     <row r="4" spans="1:2" ht="72">
       <c r="A4" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="72">
       <c r="A5" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
   </sheetData>
@@ -2741,7 +2741,7 @@
         <v>39</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -2754,18 +2754,18 @@
     </row>
     <row r="4" spans="1:2" ht="86.4">
       <c r="A4" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="86.4">
       <c r="A5" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
   </sheetData>
@@ -2798,7 +2798,7 @@
         <v>39</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -2876,7 +2876,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="9" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B2" s="2"/>
     </row>
@@ -2890,82 +2890,82 @@
     </row>
     <row r="4" spans="1:2" ht="72">
       <c r="A4" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="72">
       <c r="A5" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="72">
       <c r="A6" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="72">
       <c r="A7" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="72">
       <c r="A8" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="72">
       <c r="A9" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="72">
       <c r="A10" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="72">
       <c r="A11" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="72">
       <c r="A12" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="72">
       <c r="A13" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
   </sheetData>
@@ -2995,7 +2995,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="11" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="B2" s="2"/>
     </row>
@@ -3009,18 +3009,18 @@
     </row>
     <row r="4" spans="1:2" ht="72">
       <c r="A4" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="57.6">
       <c r="A5" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
   </sheetData>
@@ -3050,7 +3050,7 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="10" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B2" s="2"/>
     </row>
@@ -3064,75 +3064,75 @@
     </row>
     <row r="4" spans="1:3" ht="57.6">
       <c r="A4" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="57.6">
       <c r="A5" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C5" s="6"/>
     </row>
     <row r="6" spans="1:3" ht="57.6">
       <c r="A6" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="57.6">
       <c r="A7" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="57.6">
       <c r="A8" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="57.6">
       <c r="A9" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="57.6">
       <c r="A10" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="57.6">
       <c r="A11" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="57.6">
       <c r="A12" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
   </sheetData>
@@ -3166,7 +3166,7 @@
         <v>39</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -3240,7 +3240,7 @@
         <v>39</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -3321,7 +3321,7 @@
         <v>39</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -3394,7 +3394,7 @@
         <v>39</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -3475,7 +3475,7 @@
         <v>39</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -3540,7 +3540,7 @@
         <v>39</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -3605,7 +3605,7 @@
         <v>39</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -3621,7 +3621,7 @@
         <v>72</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="57.6">
@@ -3629,7 +3629,7 @@
         <v>28</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="57.6">
@@ -3637,7 +3637,7 @@
         <v>29</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="57.6">
@@ -3645,7 +3645,7 @@
         <v>30</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
   </sheetData>
